--- a/data/satisfaction_detail/2026/1-6月/特色美食廊.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/特色美食廊.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>9.34</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>9.93</v>
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.08</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>9.98</v>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.32</v>
+        <v>9.33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>9.970000000000001</v>
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9.23</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>10</v>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.44</v>
+        <v>9.51</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.07</v>
+        <v>9.08</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.98</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/data/satisfaction_detail/2026/1-6月/特色美食廊.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/特色美食廊.xlsx
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>菜品口味口相</t>
+          <t>菜品口味品相</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
